--- a/backend/data/financials_by_company/1755.HK.xlsx
+++ b/backend/data/financials_by_company/1755.HK.xlsx
@@ -662,148 +662,146 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-46255245.530798</v>
+        <v>-59230422.018509</v>
       </c>
       <c r="C2" t="n">
-        <v>0.213337</v>
+        <v>0.246667</v>
       </c>
       <c r="D2" t="n">
-        <v>970997000</v>
+        <v>1015110000</v>
       </c>
       <c r="E2" t="n">
-        <v>-216818000</v>
+        <v>-240123000</v>
       </c>
       <c r="F2" t="n">
-        <v>-216818000</v>
+        <v>-240123000</v>
       </c>
       <c r="G2" t="n">
-        <v>445045000</v>
+        <v>525455000</v>
       </c>
       <c r="H2" t="n">
-        <v>107752000</v>
+        <v>32974000</v>
       </c>
       <c r="I2" t="n">
-        <v>3985806000</v>
+        <v>3009188000</v>
       </c>
       <c r="J2" t="n">
-        <v>754179000</v>
+        <v>774987000</v>
       </c>
       <c r="K2" t="n">
-        <v>646427000</v>
+        <v>742013000</v>
       </c>
       <c r="L2" t="n">
-        <v>22124000</v>
+        <v>78115000</v>
       </c>
       <c r="M2" t="n">
-        <v>842000</v>
+        <v>337000</v>
       </c>
       <c r="N2" t="n">
-        <v>22966000</v>
+        <v>78452000</v>
       </c>
       <c r="O2" t="n">
-        <v>615607754.469202</v>
+        <v>706347577.981491</v>
       </c>
       <c r="P2" t="n">
-        <v>445045000</v>
+        <v>525455000</v>
       </c>
       <c r="Q2" t="n">
-        <v>4589663000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1376000</v>
-      </c>
+        <v>3443333000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>623676000</v>
+        <v>712711000</v>
       </c>
       <c r="T2" t="n">
-        <v>855227000</v>
+        <v>847729000</v>
       </c>
       <c r="U2" t="n">
-        <v>854816000</v>
+        <v>847729000</v>
       </c>
       <c r="V2" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="W2" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="X2" t="n">
-        <v>445045000</v>
+        <v>525455000</v>
       </c>
       <c r="Y2" t="n">
-        <v>445045000</v>
+        <v>525455000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>445045000</v>
+        <v>525455000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-62813000</v>
+        <v>-33274000</v>
       </c>
       <c r="AC2" t="n">
-        <v>507858000</v>
+        <v>558729000</v>
       </c>
       <c r="AD2" t="n">
-        <v>507858000</v>
+        <v>558729000</v>
       </c>
       <c r="AE2" t="n">
-        <v>137727000</v>
+        <v>182947000</v>
       </c>
       <c r="AF2" t="n">
-        <v>645585000</v>
+        <v>741676000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3673000</v>
+        <v>6773000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-251599000</v>
+        <v>-113541000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4138000</v>
+        <v>2309000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>255737000</v>
+        <v>111232000</v>
       </c>
       <c r="AK2" t="n">
-        <v>22124000</v>
+        <v>78115000</v>
       </c>
       <c r="AL2" t="n">
-        <v>842000</v>
+        <v>337000</v>
       </c>
       <c r="AM2" t="n">
-        <v>22966000</v>
+        <v>78452000</v>
       </c>
       <c r="AN2" t="n">
-        <v>834621000</v>
+        <v>907402000</v>
       </c>
       <c r="AO2" t="n">
-        <v>603857000</v>
+        <v>434145000</v>
       </c>
       <c r="AP2" t="n">
-        <v>645722000</v>
+        <v>458070000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>104746000</v>
+        <v>34035000</v>
       </c>
       <c r="AR2" t="n">
-        <v>540976000</v>
+        <v>424035000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1438478000</v>
+        <v>1341547000</v>
       </c>
       <c r="AT2" t="n">
-        <v>3985806000</v>
+        <v>3009188000</v>
       </c>
       <c r="AU2" t="n">
-        <v>5424284000</v>
+        <v>4350735000</v>
       </c>
       <c r="AV2" t="n">
-        <v>5424284000</v>
+        <v>4350735000</v>
       </c>
     </row>
     <row r="3">
@@ -954,146 +952,148 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-59230422.018509</v>
+        <v>-46255245.530798</v>
       </c>
       <c r="C4" t="n">
-        <v>0.246667</v>
+        <v>0.213337</v>
       </c>
       <c r="D4" t="n">
-        <v>1015110000</v>
+        <v>970997000</v>
       </c>
       <c r="E4" t="n">
-        <v>-240123000</v>
+        <v>-216818000</v>
       </c>
       <c r="F4" t="n">
-        <v>-240123000</v>
+        <v>-216818000</v>
       </c>
       <c r="G4" t="n">
-        <v>525455000</v>
+        <v>445045000</v>
       </c>
       <c r="H4" t="n">
-        <v>32974000</v>
+        <v>107752000</v>
       </c>
       <c r="I4" t="n">
-        <v>3009188000</v>
+        <v>3985806000</v>
       </c>
       <c r="J4" t="n">
-        <v>774987000</v>
+        <v>754179000</v>
       </c>
       <c r="K4" t="n">
-        <v>742013000</v>
+        <v>646427000</v>
       </c>
       <c r="L4" t="n">
-        <v>78115000</v>
+        <v>22124000</v>
       </c>
       <c r="M4" t="n">
-        <v>337000</v>
+        <v>842000</v>
       </c>
       <c r="N4" t="n">
-        <v>78452000</v>
+        <v>22966000</v>
       </c>
       <c r="O4" t="n">
-        <v>706347577.981491</v>
+        <v>615607754.469202</v>
       </c>
       <c r="P4" t="n">
-        <v>525455000</v>
+        <v>445045000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3443333000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>4589663000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1376000</v>
+      </c>
       <c r="S4" t="n">
-        <v>712711000</v>
+        <v>623676000</v>
       </c>
       <c r="T4" t="n">
-        <v>847729000</v>
+        <v>855227000</v>
       </c>
       <c r="U4" t="n">
-        <v>847729000</v>
+        <v>854816000</v>
       </c>
       <c r="V4" t="n">
-        <v>0.62</v>
+        <v>0.52</v>
       </c>
       <c r="W4" t="n">
-        <v>0.62</v>
+        <v>0.52</v>
       </c>
       <c r="X4" t="n">
-        <v>525455000</v>
+        <v>445045000</v>
       </c>
       <c r="Y4" t="n">
-        <v>525455000</v>
+        <v>445045000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>525455000</v>
+        <v>445045000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-33274000</v>
+        <v>-62813000</v>
       </c>
       <c r="AC4" t="n">
-        <v>558729000</v>
+        <v>507858000</v>
       </c>
       <c r="AD4" t="n">
-        <v>558729000</v>
+        <v>507858000</v>
       </c>
       <c r="AE4" t="n">
-        <v>182947000</v>
+        <v>137727000</v>
       </c>
       <c r="AF4" t="n">
-        <v>741676000</v>
+        <v>645585000</v>
       </c>
       <c r="AG4" t="n">
-        <v>6773000</v>
+        <v>-3673000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-113541000</v>
+        <v>-251599000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2309000</v>
+        <v>-4138000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>111232000</v>
+        <v>255737000</v>
       </c>
       <c r="AK4" t="n">
-        <v>78115000</v>
+        <v>22124000</v>
       </c>
       <c r="AL4" t="n">
-        <v>337000</v>
+        <v>842000</v>
       </c>
       <c r="AM4" t="n">
-        <v>78452000</v>
+        <v>22966000</v>
       </c>
       <c r="AN4" t="n">
-        <v>907402000</v>
+        <v>834621000</v>
       </c>
       <c r="AO4" t="n">
-        <v>434145000</v>
+        <v>603857000</v>
       </c>
       <c r="AP4" t="n">
-        <v>458070000</v>
+        <v>645722000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>34035000</v>
+        <v>104746000</v>
       </c>
       <c r="AR4" t="n">
-        <v>424035000</v>
+        <v>540976000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1341547000</v>
+        <v>1438478000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3009188000</v>
+        <v>3985806000</v>
       </c>
       <c r="AU4" t="n">
-        <v>4350735000</v>
+        <v>5424284000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4350735000</v>
+        <v>5424284000</v>
       </c>
     </row>
   </sheetData>
@@ -1459,208 +1459,206 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>871331000</v>
+        <v>870134000</v>
       </c>
       <c r="C2" t="n">
-        <v>871331000</v>
+        <v>870134000</v>
       </c>
       <c r="D2" t="n">
-        <v>15271000</v>
+        <v>14439000</v>
       </c>
       <c r="E2" t="n">
-        <v>2053835000</v>
+        <v>1555595000</v>
       </c>
       <c r="F2" t="n">
-        <v>2903765000</v>
+        <v>2283920000</v>
       </c>
       <c r="G2" t="n">
-        <v>2396889000</v>
+        <v>1654975000</v>
       </c>
       <c r="H2" t="n">
-        <v>2053835000</v>
+        <v>1555595000</v>
       </c>
       <c r="I2" t="n">
-        <v>15271000</v>
+        <v>14439000</v>
       </c>
       <c r="J2" t="n">
-        <v>2903765000</v>
+        <v>2283920000</v>
       </c>
       <c r="K2" t="n">
-        <v>2903765000</v>
+        <v>2283920000</v>
       </c>
       <c r="L2" t="n">
-        <v>3291208000</v>
+        <v>2524632000</v>
       </c>
       <c r="M2" t="n">
-        <v>387443000</v>
+        <v>240712000</v>
       </c>
       <c r="N2" t="n">
-        <v>2903765000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-213776000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2316390000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>632053000</v>
-      </c>
+        <v>2283920000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>59980000</v>
+        <v>59900000</v>
       </c>
       <c r="S2" t="n">
-        <v>59980000</v>
+        <v>59900000</v>
       </c>
       <c r="T2" t="n">
-        <v>3391435000</v>
+        <v>2885013000</v>
       </c>
       <c r="U2" t="n">
-        <v>236043000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
+        <v>203606000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>112924000</v>
+        <v>92857000</v>
       </c>
       <c r="X2" t="n">
-        <v>111326000</v>
+        <v>97375000</v>
       </c>
       <c r="Y2" t="n">
-        <v>7693000</v>
+        <v>11310000</v>
       </c>
       <c r="Z2" t="n">
-        <v>7693000</v>
+        <v>11310000</v>
       </c>
       <c r="AA2" t="n">
-        <v>4100000</v>
+        <v>2064000</v>
       </c>
       <c r="AB2" t="n">
-        <v>3155392000</v>
+        <v>2681407000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7578000</v>
+        <v>3129000</v>
       </c>
       <c r="AD2" t="n">
-        <v>7578000</v>
+        <v>3129000</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1706351000</v>
+        <v>1512478000</v>
       </c>
       <c r="AG2" t="n">
-        <v>893945000</v>
+        <v>718504000</v>
       </c>
       <c r="AH2" t="n">
-        <v>27467000</v>
+        <v>25293000</v>
       </c>
       <c r="AI2" t="n">
-        <v>374345000</v>
+        <v>231806000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>410594000</v>
+        <v>536875000</v>
       </c>
       <c r="AK2" t="n">
-        <v>6682643000</v>
+        <v>5409645000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1130362000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>1073263000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1944000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>106927000</v>
+        <v>54509000</v>
       </c>
       <c r="AO2" t="n">
-        <v>75624000</v>
+        <v>205873000</v>
       </c>
       <c r="AP2" t="n">
-        <v>75624000</v>
+        <v>205873000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5683000</v>
+        <v>4000000</v>
       </c>
       <c r="AR2" t="n">
-        <v>5683000</v>
+        <v>4000000</v>
       </c>
       <c r="AS2" t="n">
-        <v>849930000</v>
+        <v>728325000</v>
       </c>
       <c r="AT2" t="n">
-        <v>442561000</v>
+        <v>377347000</v>
       </c>
       <c r="AU2" t="n">
-        <v>407369000</v>
+        <v>350978000</v>
       </c>
       <c r="AV2" t="n">
-        <v>92198000</v>
+        <v>78612000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-72826000</v>
+        <v>-19163000</v>
       </c>
       <c r="AX2" t="n">
-        <v>165024000</v>
+        <v>97775000</v>
       </c>
       <c r="AY2" t="n">
-        <v>45422000</v>
+        <v>41034000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>86831000</v>
+        <v>49084000</v>
       </c>
       <c r="BA2" t="n">
-        <v>32771000</v>
+        <v>7657000</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>5552281000</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
+        <v>4336382000</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>493003000</v>
+      </c>
       <c r="BE2" t="n">
-        <v>39614000</v>
+        <v>28301000</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>223000</v>
+        <v>219000</v>
       </c>
       <c r="BH2" t="n">
-        <v>3519000</v>
+        <v>1600000</v>
       </c>
       <c r="BI2" t="n">
-        <v>35872000</v>
+        <v>26482000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1282570000</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
+        <v>375068000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>15728000</v>
+      </c>
       <c r="BL2" t="n">
-        <v>1796855000</v>
+        <v>622758000</v>
       </c>
       <c r="BM2" t="n">
-        <v>-279581000</v>
+        <v>-87680000</v>
       </c>
       <c r="BN2" t="n">
-        <v>2076436000</v>
+        <v>710438000</v>
       </c>
       <c r="BO2" t="n">
-        <v>2433242000</v>
+        <v>2801524000</v>
       </c>
       <c r="BP2" t="n">
-        <v>505959000</v>
+        <v>297422000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1927283000</v>
+        <v>2504102000</v>
       </c>
       <c r="BR2" t="n">
-        <v>1927283000</v>
+        <v>2504102000</v>
       </c>
     </row>
     <row r="3">
@@ -1877,206 +1875,208 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>870134000</v>
+        <v>871331000</v>
       </c>
       <c r="C4" t="n">
-        <v>870134000</v>
+        <v>871331000</v>
       </c>
       <c r="D4" t="n">
-        <v>14439000</v>
+        <v>15271000</v>
       </c>
       <c r="E4" t="n">
-        <v>1555595000</v>
+        <v>2053835000</v>
       </c>
       <c r="F4" t="n">
-        <v>2283920000</v>
+        <v>2903765000</v>
       </c>
       <c r="G4" t="n">
-        <v>1654975000</v>
+        <v>2396889000</v>
       </c>
       <c r="H4" t="n">
-        <v>1555595000</v>
+        <v>2053835000</v>
       </c>
       <c r="I4" t="n">
-        <v>14439000</v>
+        <v>15271000</v>
       </c>
       <c r="J4" t="n">
-        <v>2283920000</v>
+        <v>2903765000</v>
       </c>
       <c r="K4" t="n">
-        <v>2283920000</v>
+        <v>2903765000</v>
       </c>
       <c r="L4" t="n">
-        <v>2524632000</v>
+        <v>3291208000</v>
       </c>
       <c r="M4" t="n">
-        <v>240712000</v>
+        <v>387443000</v>
       </c>
       <c r="N4" t="n">
-        <v>2283920000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>2903765000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-213776000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2316390000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>632053000</v>
+      </c>
       <c r="R4" t="n">
-        <v>59900000</v>
+        <v>59980000</v>
       </c>
       <c r="S4" t="n">
-        <v>59900000</v>
+        <v>59980000</v>
       </c>
       <c r="T4" t="n">
-        <v>2885013000</v>
+        <v>3391435000</v>
       </c>
       <c r="U4" t="n">
-        <v>203606000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>236043000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
       <c r="W4" t="n">
-        <v>92857000</v>
+        <v>112924000</v>
       </c>
       <c r="X4" t="n">
-        <v>97375000</v>
+        <v>111326000</v>
       </c>
       <c r="Y4" t="n">
-        <v>11310000</v>
+        <v>7693000</v>
       </c>
       <c r="Z4" t="n">
-        <v>11310000</v>
+        <v>7693000</v>
       </c>
       <c r="AA4" t="n">
-        <v>2064000</v>
+        <v>4100000</v>
       </c>
       <c r="AB4" t="n">
-        <v>2681407000</v>
+        <v>3155392000</v>
       </c>
       <c r="AC4" t="n">
-        <v>3129000</v>
+        <v>7578000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3129000</v>
+        <v>7578000</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1512478000</v>
+        <v>1706351000</v>
       </c>
       <c r="AG4" t="n">
-        <v>718504000</v>
+        <v>893945000</v>
       </c>
       <c r="AH4" t="n">
-        <v>25293000</v>
+        <v>27467000</v>
       </c>
       <c r="AI4" t="n">
-        <v>231806000</v>
+        <v>374345000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>536875000</v>
+        <v>410594000</v>
       </c>
       <c r="AK4" t="n">
-        <v>5409645000</v>
+        <v>6682643000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1073263000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1944000</v>
-      </c>
+        <v>1130362000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>54509000</v>
+        <v>106927000</v>
       </c>
       <c r="AO4" t="n">
-        <v>205873000</v>
+        <v>75624000</v>
       </c>
       <c r="AP4" t="n">
-        <v>205873000</v>
+        <v>75624000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4000000</v>
+        <v>5683000</v>
       </c>
       <c r="AR4" t="n">
-        <v>4000000</v>
+        <v>5683000</v>
       </c>
       <c r="AS4" t="n">
-        <v>728325000</v>
+        <v>849930000</v>
       </c>
       <c r="AT4" t="n">
-        <v>377347000</v>
+        <v>442561000</v>
       </c>
       <c r="AU4" t="n">
-        <v>350978000</v>
+        <v>407369000</v>
       </c>
       <c r="AV4" t="n">
-        <v>78612000</v>
+        <v>92198000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-19163000</v>
+        <v>-72826000</v>
       </c>
       <c r="AX4" t="n">
-        <v>97775000</v>
+        <v>165024000</v>
       </c>
       <c r="AY4" t="n">
-        <v>41034000</v>
+        <v>45422000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>49084000</v>
+        <v>86831000</v>
       </c>
       <c r="BA4" t="n">
-        <v>7657000</v>
+        <v>32771000</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>4336382000</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>493003000</v>
-      </c>
+        <v>5552281000</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
-        <v>28301000</v>
+        <v>39614000</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>219000</v>
+        <v>223000</v>
       </c>
       <c r="BH4" t="n">
-        <v>1600000</v>
+        <v>3519000</v>
       </c>
       <c r="BI4" t="n">
-        <v>26482000</v>
+        <v>35872000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>375068000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>15728000</v>
-      </c>
+        <v>1282570000</v>
+      </c>
+      <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="n">
-        <v>622758000</v>
+        <v>1796855000</v>
       </c>
       <c r="BM4" t="n">
-        <v>-87680000</v>
+        <v>-279581000</v>
       </c>
       <c r="BN4" t="n">
-        <v>710438000</v>
+        <v>2076436000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2801524000</v>
+        <v>2433242000</v>
       </c>
       <c r="BP4" t="n">
-        <v>297422000</v>
+        <v>505959000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2504102000</v>
+        <v>1927283000</v>
       </c>
       <c r="BR4" t="n">
-        <v>2504102000</v>
+        <v>1927283000</v>
       </c>
     </row>
   </sheetData>
@@ -2327,141 +2327,145 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>390330000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>703835000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-48599000</v>
+      </c>
       <c r="D2" t="n">
-        <v>-18265000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3182000</v>
+        <v>759364000</v>
       </c>
       <c r="F2" t="n">
-        <v>-33380000</v>
+        <v>-51499000</v>
       </c>
       <c r="G2" t="n">
-        <v>1927283000</v>
+        <v>2504102000</v>
       </c>
       <c r="H2" t="n">
-        <v>1973696000</v>
+        <v>1882136000</v>
       </c>
       <c r="I2" t="n">
-        <v>9361000</v>
+        <v>-10491000</v>
       </c>
       <c r="J2" t="n">
-        <v>-55774000</v>
+        <v>632457000</v>
       </c>
       <c r="K2" t="n">
-        <v>-175253000</v>
+        <v>468217000</v>
       </c>
       <c r="L2" t="n">
-        <v>-4559000</v>
+        <v>6932000</v>
       </c>
       <c r="M2" t="n">
-        <v>3182000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>710765000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-48599000</v>
+      </c>
       <c r="O2" t="n">
-        <v>3182000</v>
+        <v>759364000</v>
       </c>
       <c r="P2" t="n">
-        <v>-18265000</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-18265000</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-18265000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-304231000</v>
+        <v>-591094000</v>
       </c>
       <c r="T2" t="n">
-        <v>5620000</v>
+        <v>49150000</v>
       </c>
       <c r="U2" t="n">
-        <v>-203024000</v>
+        <v>-406817000</v>
       </c>
       <c r="V2" t="n">
-        <v>130307000</v>
+        <v>922616000</v>
       </c>
       <c r="W2" t="n">
-        <v>-333331000</v>
+        <v>-1329433000</v>
       </c>
       <c r="X2" t="n">
-        <v>-80290000</v>
+        <v>-184629000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-80290000</v>
+        <v>-184629000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-7218000</v>
+        <v>-7740000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-7218000</v>
+        <v>-7740000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-19319000</v>
+        <v>-41058000</v>
       </c>
       <c r="AC2" t="n">
-        <v>6843000</v>
+        <v>2701000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-26162000</v>
+        <v>-43759000</v>
       </c>
       <c r="AE2" t="n">
-        <v>423710000</v>
+        <v>755334000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-145091000</v>
+        <v>-158109000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-475607000</v>
+        <v>-68238000</v>
       </c>
       <c r="AH2" t="n">
-        <v>63034000</v>
+        <v>131743000</v>
       </c>
       <c r="AI2" t="n">
-        <v>12641000</v>
+        <v>306647000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>89467000</v>
+        <v>-233407000</v>
       </c>
       <c r="AK2" t="n">
-        <v>4616000</v>
+        <v>-10149000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-646363000</v>
+        <v>-263330000</v>
       </c>
       <c r="AM2" t="n">
-        <v>657000</v>
+        <v>-48706000</v>
       </c>
       <c r="AN2" t="n">
-        <v>6069000</v>
+        <v>8742000</v>
       </c>
       <c r="AO2" t="n">
-        <v>107752000</v>
+        <v>32974000</v>
       </c>
       <c r="AP2" t="n">
-        <v>68336000</v>
+        <v>18504000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>39416000</v>
+        <v>14470000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-34781000</v>
+        <v>126582000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-9361000</v>
+        <v>10491000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-4138000</v>
+        <v>-1310000</v>
       </c>
       <c r="AU2" t="n">
-        <v>645585000</v>
+        <v>741676000</v>
       </c>
     </row>
     <row r="3">
@@ -2609,145 +2613,141 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>703835000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-48599000</v>
-      </c>
+        <v>390330000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-18265000</v>
       </c>
       <c r="E4" t="n">
-        <v>759364000</v>
+        <v>3182000</v>
       </c>
       <c r="F4" t="n">
-        <v>-51499000</v>
+        <v>-33380000</v>
       </c>
       <c r="G4" t="n">
-        <v>2504102000</v>
+        <v>1927283000</v>
       </c>
       <c r="H4" t="n">
-        <v>1882136000</v>
+        <v>1973696000</v>
       </c>
       <c r="I4" t="n">
-        <v>-10491000</v>
+        <v>9361000</v>
       </c>
       <c r="J4" t="n">
-        <v>632457000</v>
+        <v>-55774000</v>
       </c>
       <c r="K4" t="n">
-        <v>468217000</v>
+        <v>-175253000</v>
       </c>
       <c r="L4" t="n">
-        <v>6932000</v>
+        <v>-4559000</v>
       </c>
       <c r="M4" t="n">
-        <v>710765000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-48599000</v>
-      </c>
+        <v>3182000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>759364000</v>
+        <v>3182000</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-18265000</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-18265000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-18265000</v>
       </c>
       <c r="S4" t="n">
-        <v>-591094000</v>
+        <v>-304231000</v>
       </c>
       <c r="T4" t="n">
-        <v>49150000</v>
+        <v>5620000</v>
       </c>
       <c r="U4" t="n">
-        <v>-406817000</v>
+        <v>-203024000</v>
       </c>
       <c r="V4" t="n">
-        <v>922616000</v>
+        <v>130307000</v>
       </c>
       <c r="W4" t="n">
-        <v>-1329433000</v>
+        <v>-333331000</v>
       </c>
       <c r="X4" t="n">
-        <v>-184629000</v>
+        <v>-80290000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-184629000</v>
+        <v>-80290000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-7740000</v>
+        <v>-7218000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-7740000</v>
+        <v>-7218000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-41058000</v>
+        <v>-19319000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2701000</v>
+        <v>6843000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-43759000</v>
+        <v>-26162000</v>
       </c>
       <c r="AE4" t="n">
-        <v>755334000</v>
+        <v>423710000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-158109000</v>
+        <v>-145091000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-68238000</v>
+        <v>-475607000</v>
       </c>
       <c r="AH4" t="n">
-        <v>131743000</v>
+        <v>63034000</v>
       </c>
       <c r="AI4" t="n">
-        <v>306647000</v>
+        <v>12641000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-233407000</v>
+        <v>89467000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-10149000</v>
+        <v>4616000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-263330000</v>
+        <v>-646363000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-48706000</v>
+        <v>657000</v>
       </c>
       <c r="AN4" t="n">
-        <v>8742000</v>
+        <v>6069000</v>
       </c>
       <c r="AO4" t="n">
-        <v>32974000</v>
+        <v>107752000</v>
       </c>
       <c r="AP4" t="n">
-        <v>18504000</v>
+        <v>68336000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14470000</v>
+        <v>39416000</v>
       </c>
       <c r="AR4" t="n">
-        <v>126582000</v>
+        <v>-34781000</v>
       </c>
       <c r="AS4" t="n">
-        <v>10491000</v>
+        <v>-9361000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1310000</v>
+        <v>-4138000</v>
       </c>
       <c r="AU4" t="n">
-        <v>741676000</v>
+        <v>645585000</v>
       </c>
     </row>
   </sheetData>
@@ -3317,202 +3317,202 @@
       </c>
       <c r="DG1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EU1" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Xiaoming  Qi', 'age': 55, 'title': 'Chairman, CEO &amp; GM', 'yearBorn': 1970, 'fiscalYear': 2023, 'totalPay': 4830700, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Qianqian  Wu', 'age': 40, 'title': 'Executive Director', 'yearBorn': 1985, 'fiscalYear': 2023, 'totalPay': 1208254, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yingjie  Liu', 'age': 49, 'title': 'Chief Financial Officer', 'yearBorn': 1976, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bingli  Lu', 'age': 43, 'title': 'Chief Technology Officer', 'yearBorn': 1982, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Pan  Yuncheng', 'title': 'Investor Relations Manager', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liang  Gong', 'age': 38, 'title': 'Chief Human Resource Officer', 'yearBorn': 1987, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jianfeng  You', 'age': 46, 'title': 'Chief Strategy Officer', 'yearBorn': 1979, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zixuan  Hu', 'age': 36, 'title': 'Chief Digital Officer', 'yearBorn': 1989, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Peng  Chen', 'age': 51, 'title': 'Joint Company Secretary', 'yearBorn': 1974, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ka Yan  Tsui', 'title': 'Joint Company Secretary', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Xiaoming  Qi', 'age': 55, 'title': 'Chairman, CEO &amp; GM', 'yearBorn': 1970, 'fiscalYear': 2023, 'totalPay': 4826851, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Qianqian  Wu', 'age': 40, 'title': 'Executive Director', 'yearBorn': 1985, 'fiscalYear': 2023, 'totalPay': 1207291, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yingjie  Liu', 'age': 49, 'title': 'Chief Financial Officer', 'yearBorn': 1976, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bingli  Lu', 'age': 43, 'title': 'Chief Technology Officer', 'yearBorn': 1982, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Pan  Yuncheng', 'title': 'Investor Relations Manager', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liang  Gong', 'age': 38, 'title': 'Chief Human Resource Officer', 'yearBorn': 1987, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jianfeng  You', 'age': 46, 'title': 'Chief Strategy Officer', 'yearBorn': 1979, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zixuan  Hu', 'age': 36, 'title': 'Chief Digital Officer', 'yearBorn': 1989, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Peng  Chen', 'age': 51, 'title': 'Joint Company Secretary', 'yearBorn': 1974, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ka Yan  Tsui', 'title': 'Joint Company Secretary', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3643,7 +3643,7 @@
         <v>3.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.043</v>
+        <v>1.049</v>
       </c>
       <c r="AF2" t="n">
         <v>4.5901637</v>
@@ -3741,10 +3741,10 @@
         <v>871331000</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.49927</v>
+        <v>2.4979436</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.1203271</v>
+        <v>1.120922</v>
       </c>
       <c r="BM2" t="n">
         <v>1735603200</v>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BX2" t="n">
         <v>0.22506</v>
@@ -3902,71 +3902,65 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
+      <c r="DG2" t="n">
+        <v>-0.1500001</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>2.8 - 2.9</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>2.8 - 2.9</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.10000014</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.034482807</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1724852385</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1724852385</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
         <v>1541467800000</v>
       </c>
-      <c r="DJ2" t="n">
-        <v>-0.1500001</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>2.8 - 2.9</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>2.8 - 2.9</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.10000014</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.034482807</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1724852385</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>S-ENJOY SERVICE</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>S-Enjoy Service Group Co., Limited</t>
-        </is>
-      </c>
       <c r="DW2" t="n">
-        <v>1724852385</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
+        <v>-5.0847487</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>2.8</v>
       </c>
       <c r="DY2" t="n">
         <v>0.61</v>
@@ -3998,53 +3992,59 @@
       <c r="EH2" t="n">
         <v>15</v>
       </c>
-      <c r="EI2" t="b">
-        <v>0</v>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="EJ2" t="n">
-        <v>-5.0847487</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>2.8</v>
+        <v>1743408508</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EM2" t="n">
-        <v>1743408508</v>
+          <t>finmb_587381213</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>finmb_587381213</t>
-        </is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EO2" t="n">
+        <v>28800000</v>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="ER2" t="n">
-        <v>28800000</v>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>S-ENJOY SERVICE</t>
+        </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="ET2" t="b">
-        <v>0</v>
+          <t>S-Enjoy Service Group Co., Limited</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="EU2" t="inlineStr"/>
     </row>
